--- a/sheets/Libetee_8月スケジュール_公式.xlsx
+++ b/sheets/Libetee_8月スケジュール_公式.xlsx
@@ -17,11 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="m/d(aaa)"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="¥#,##0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="m/d(aaa)"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="¥#,##0"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -101,7 +100,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -123,18 +122,62 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -143,16 +186,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -161,16 +204,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -179,16 +222,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,16 +240,16 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -215,22 +258,55 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -681,8 +757,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>46235</v>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>8/1(土)</t>
+        </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -699,10 +777,10 @@
           <t>ワンダフルデー</t>
         </is>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="41" t="n">
         <v>1.46</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="42" t="n">
         <v>1081629</v>
       </c>
       <c r="G4" s="9" t="n">
@@ -711,14 +789,16 @@
       <c r="H4" s="9" t="n">
         <v>40000</v>
       </c>
-      <c r="I4" s="8" t="n">
+      <c r="I4" s="42" t="n">
         <v>1072855</v>
       </c>
       <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
-        <v>46236</v>
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>8/2(日)</t>
+        </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
@@ -735,10 +815,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G5" s="15" t="n">
@@ -747,7 +827,7 @@
       <c r="H5" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="I5" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J5" s="12" t="inlineStr">
@@ -757,8 +837,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
-        <v>46237</v>
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>8/3(月)</t>
+        </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
@@ -775,10 +857,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G6" s="15" t="n">
@@ -787,14 +869,16 @@
       <c r="H6" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I6" s="14" t="n">
+      <c r="I6" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>46238</v>
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>8/4(火)</t>
+        </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
@@ -811,10 +895,10 @@
           <t>お買い物マラソン</t>
         </is>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="45" t="n">
         <v>1.11</v>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="46" t="n">
         <v>824846</v>
       </c>
       <c r="G7" s="21" t="n">
@@ -823,7 +907,7 @@
       <c r="H7" s="21" t="n">
         <v>40000</v>
       </c>
-      <c r="I7" s="20" t="n">
+      <c r="I7" s="46" t="n">
         <v>630136</v>
       </c>
       <c r="J7" s="18" t="inlineStr">
@@ -833,8 +917,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="n">
-        <v>46239</v>
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>8/5(水)</t>
+        </is>
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -851,10 +937,10 @@
           <t>マラソン×5と0 かぶり</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="47" t="n">
         <v>3.02</v>
       </c>
-      <c r="F8" s="26" t="n">
+      <c r="F8" s="48" t="n">
         <v>2234584</v>
       </c>
       <c r="G8" s="27" t="n">
@@ -863,7 +949,7 @@
       <c r="H8" s="27" t="n">
         <v>40000</v>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I8" s="48" t="n">
         <v>1339254</v>
       </c>
       <c r="J8" s="24" t="inlineStr">
@@ -873,8 +959,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>46240</v>
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>8/6(木)</t>
+        </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
@@ -891,10 +979,10 @@
           <t>お買い物マラソン</t>
         </is>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="45" t="n">
         <v>1.11</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="46" t="n">
         <v>824846</v>
       </c>
       <c r="G9" s="21" t="n">
@@ -903,14 +991,16 @@
       <c r="H9" s="21" t="n">
         <v>40000</v>
       </c>
-      <c r="I9" s="20" t="n">
+      <c r="I9" s="46" t="n">
         <v>630136</v>
       </c>
       <c r="J9" s="18" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>46241</v>
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>8/7(金)</t>
+        </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
@@ -927,10 +1017,10 @@
           <t>お買い物マラソン</t>
         </is>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="45" t="n">
         <v>1.11</v>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="46" t="n">
         <v>824846</v>
       </c>
       <c r="G10" s="21" t="n">
@@ -939,14 +1029,16 @@
       <c r="H10" s="21" t="n">
         <v>40000</v>
       </c>
-      <c r="I10" s="20" t="n">
+      <c r="I10" s="46" t="n">
         <v>630136</v>
       </c>
       <c r="J10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>46242</v>
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>8/8(土)</t>
+        </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
@@ -963,10 +1055,10 @@
           <t>お買い物マラソン</t>
         </is>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="45" t="n">
         <v>1.11</v>
       </c>
-      <c r="F11" s="20" t="n">
+      <c r="F11" s="46" t="n">
         <v>824846</v>
       </c>
       <c r="G11" s="21" t="n">
@@ -975,14 +1067,16 @@
       <c r="H11" s="21" t="n">
         <v>40000</v>
       </c>
-      <c r="I11" s="20" t="n">
+      <c r="I11" s="46" t="n">
         <v>630136</v>
       </c>
       <c r="J11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>46243</v>
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>8/9(日)</t>
+        </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
@@ -999,10 +1093,10 @@
           <t>お買い物マラソン</t>
         </is>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="45" t="n">
         <v>1.11</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="46" t="n">
         <v>824846</v>
       </c>
       <c r="G12" s="21" t="n">
@@ -1011,14 +1105,16 @@
       <c r="H12" s="21" t="n">
         <v>40000</v>
       </c>
-      <c r="I12" s="20" t="n">
+      <c r="I12" s="46" t="n">
         <v>630136</v>
       </c>
       <c r="J12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="22" t="n">
-        <v>46244</v>
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>8/10(月)</t>
+        </is>
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -1035,10 +1131,10 @@
           <t>マラソン×5と0 かぶり</t>
         </is>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="47" t="n">
         <v>3.02</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="48" t="n">
         <v>2234584</v>
       </c>
       <c r="G13" s="27" t="n">
@@ -1047,7 +1143,7 @@
       <c r="H13" s="27" t="n">
         <v>40000</v>
       </c>
-      <c r="I13" s="26" t="n">
+      <c r="I13" s="48" t="n">
         <v>1339254</v>
       </c>
       <c r="J13" s="24" t="inlineStr">
@@ -1057,8 +1153,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n">
-        <v>46245</v>
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>8/11(火)</t>
+        </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
@@ -1075,10 +1173,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G14" s="15" t="n">
@@ -1087,7 +1185,7 @@
       <c r="H14" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I14" s="14" t="n">
+      <c r="I14" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J14" s="12" t="inlineStr">
@@ -1097,8 +1195,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
-        <v>46246</v>
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>8/12(水)</t>
+        </is>
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
@@ -1115,10 +1215,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G15" s="15" t="n">
@@ -1127,14 +1227,16 @@
       <c r="H15" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I15" s="14" t="n">
+      <c r="I15" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n">
-        <v>46247</v>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>8/13(木)</t>
+        </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
@@ -1151,10 +1253,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G16" s="15" t="n">
@@ -1163,14 +1265,16 @@
       <c r="H16" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I16" s="14" t="n">
+      <c r="I16" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
-        <v>46248</v>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>8/14(金)</t>
+        </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
@@ -1187,10 +1291,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G17" s="15" t="n">
@@ -1199,14 +1303,16 @@
       <c r="H17" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I17" s="14" t="n">
+      <c r="I17" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="n">
-        <v>46249</v>
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>8/15(土)</t>
+        </is>
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
@@ -1223,10 +1329,10 @@
           <t>5と0のつく日</t>
         </is>
       </c>
-      <c r="E18" s="31" t="n">
+      <c r="E18" s="49" t="n">
         <v>2.2</v>
       </c>
-      <c r="F18" s="32" t="n">
+      <c r="F18" s="50" t="n">
         <v>1631874</v>
       </c>
       <c r="G18" s="33" t="n">
@@ -1235,14 +1341,16 @@
       <c r="H18" s="33" t="n">
         <v>40000</v>
       </c>
-      <c r="I18" s="32" t="n">
+      <c r="I18" s="50" t="n">
         <v>925842</v>
       </c>
       <c r="J18" s="30" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
-        <v>46250</v>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>8/16(日)</t>
+        </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
@@ -1259,10 +1367,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G19" s="15" t="n">
@@ -1271,14 +1379,16 @@
       <c r="H19" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="I19" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
-        <v>46251</v>
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>8/17(月)</t>
+        </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
@@ -1295,10 +1405,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E20" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G20" s="15" t="n">
@@ -1307,14 +1417,16 @@
       <c r="H20" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I20" s="14" t="n">
+      <c r="I20" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
-        <v>46252</v>
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>8/18(火)</t>
+        </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
@@ -1331,10 +1443,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="14" t="n">
+      <c r="F21" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G21" s="15" t="n">
@@ -1343,7 +1455,7 @@
       <c r="H21" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I21" s="14" t="n">
+      <c r="I21" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J21" s="12" t="inlineStr">
@@ -1353,8 +1465,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>46253</v>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>8/19(水)</t>
+        </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
@@ -1371,10 +1485,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="14" t="n">
+      <c r="F22" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G22" s="15" t="n">
@@ -1383,14 +1497,16 @@
       <c r="H22" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I22" s="14" t="n">
+      <c r="I22" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="n">
-        <v>46254</v>
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>8/20(木)</t>
+        </is>
       </c>
       <c r="B23" s="29" t="inlineStr">
         <is>
@@ -1407,10 +1523,10 @@
           <t>5と0のつく日</t>
         </is>
       </c>
-      <c r="E23" s="31" t="n">
+      <c r="E23" s="49" t="n">
         <v>2.2</v>
       </c>
-      <c r="F23" s="32" t="n">
+      <c r="F23" s="50" t="n">
         <v>1631874</v>
       </c>
       <c r="G23" s="33" t="n">
@@ -1419,14 +1535,16 @@
       <c r="H23" s="33" t="n">
         <v>40000</v>
       </c>
-      <c r="I23" s="32" t="n">
+      <c r="I23" s="50" t="n">
         <v>925842</v>
       </c>
       <c r="J23" s="30" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>46255</v>
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>8/21(金)</t>
+        </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
@@ -1443,10 +1561,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="14" t="n">
+      <c r="F24" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G24" s="15" t="n">
@@ -1455,14 +1573,16 @@
       <c r="H24" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I24" s="14" t="n">
+      <c r="I24" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>46256</v>
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>8/22(土)</t>
+        </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
@@ -1479,10 +1599,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="14" t="n">
+      <c r="F25" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G25" s="15" t="n">
@@ -1491,7 +1611,7 @@
       <c r="H25" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I25" s="14" t="n">
+      <c r="I25" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J25" s="12" t="inlineStr">
@@ -1501,8 +1621,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n">
-        <v>46257</v>
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>8/23(日)</t>
+        </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
@@ -1519,10 +1641,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="F26" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G26" s="15" t="n">
@@ -1531,14 +1653,16 @@
       <c r="H26" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I26" s="14" t="n">
+      <c r="I26" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="n">
-        <v>46258</v>
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>8/24(月)</t>
+        </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
@@ -1555,10 +1679,10 @@
           <t>お買い物マラソン</t>
         </is>
       </c>
-      <c r="E27" s="19" t="n">
+      <c r="E27" s="45" t="n">
         <v>1.11</v>
       </c>
-      <c r="F27" s="20" t="n">
+      <c r="F27" s="46" t="n">
         <v>824846</v>
       </c>
       <c r="G27" s="21" t="n">
@@ -1567,7 +1691,7 @@
       <c r="H27" s="21" t="n">
         <v>40000</v>
       </c>
-      <c r="I27" s="20" t="n">
+      <c r="I27" s="46" t="n">
         <v>630136</v>
       </c>
       <c r="J27" s="18" t="inlineStr">
@@ -1577,8 +1701,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="n">
-        <v>46259</v>
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>8/25(火)</t>
+        </is>
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
@@ -1595,10 +1721,10 @@
           <t>マラソン×5と0 かぶり</t>
         </is>
       </c>
-      <c r="E28" s="25" t="n">
+      <c r="E28" s="47" t="n">
         <v>3.02</v>
       </c>
-      <c r="F28" s="26" t="n">
+      <c r="F28" s="48" t="n">
         <v>2234584</v>
       </c>
       <c r="G28" s="27" t="n">
@@ -1607,7 +1733,7 @@
       <c r="H28" s="27" t="n">
         <v>40000</v>
       </c>
-      <c r="I28" s="26" t="n">
+      <c r="I28" s="48" t="n">
         <v>1339254</v>
       </c>
       <c r="J28" s="24" t="inlineStr">
@@ -1617,8 +1743,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="n">
-        <v>46260</v>
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>8/26(水)</t>
+        </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
@@ -1635,10 +1763,10 @@
           <t>お買い物マラソン</t>
         </is>
       </c>
-      <c r="E29" s="19" t="n">
+      <c r="E29" s="45" t="n">
         <v>1.11</v>
       </c>
-      <c r="F29" s="20" t="n">
+      <c r="F29" s="46" t="n">
         <v>824846</v>
       </c>
       <c r="G29" s="21" t="n">
@@ -1647,14 +1775,16 @@
       <c r="H29" s="21" t="n">
         <v>40000</v>
       </c>
-      <c r="I29" s="20" t="n">
+      <c r="I29" s="46" t="n">
         <v>630136</v>
       </c>
       <c r="J29" s="18" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n">
-        <v>46261</v>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>8/27(木)</t>
+        </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
@@ -1671,10 +1801,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="14" t="n">
+      <c r="F30" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G30" s="15" t="n">
@@ -1683,7 +1813,7 @@
       <c r="H30" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I30" s="14" t="n">
+      <c r="I30" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J30" s="12" t="inlineStr">
@@ -1693,8 +1823,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
-        <v>46262</v>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>8/28(金)</t>
+        </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
@@ -1711,10 +1843,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="14" t="n">
+      <c r="F31" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G31" s="15" t="n">
@@ -1723,14 +1855,16 @@
       <c r="H31" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I31" s="14" t="n">
+      <c r="I31" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>46263</v>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>8/29(土)</t>
+        </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
@@ -1747,10 +1881,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="14" t="n">
+      <c r="F32" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G32" s="15" t="n">
@@ -1759,14 +1893,16 @@
       <c r="H32" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I32" s="14" t="n">
+      <c r="I32" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="28" t="n">
-        <v>46264</v>
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>8/30(日)</t>
+        </is>
       </c>
       <c r="B33" s="29" t="inlineStr">
         <is>
@@ -1783,10 +1919,10 @@
           <t>5と0のつく日</t>
         </is>
       </c>
-      <c r="E33" s="31" t="n">
+      <c r="E33" s="49" t="n">
         <v>2.2</v>
       </c>
-      <c r="F33" s="32" t="n">
+      <c r="F33" s="50" t="n">
         <v>1631874</v>
       </c>
       <c r="G33" s="33" t="n">
@@ -1795,14 +1931,16 @@
       <c r="H33" s="33" t="n">
         <v>40000</v>
       </c>
-      <c r="I33" s="32" t="n">
+      <c r="I33" s="50" t="n">
         <v>925842</v>
       </c>
       <c r="J33" s="30" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n">
-        <v>46265</v>
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>8/31(月)</t>
+        </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
@@ -1819,10 +1957,10 @@
           <t>平日</t>
         </is>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="14" t="n">
+      <c r="F34" s="44" t="n">
         <v>740103</v>
       </c>
       <c r="G34" s="15" t="n">
@@ -1831,7 +1969,7 @@
       <c r="H34" s="15" t="n">
         <v>15000</v>
       </c>
-      <c r="I34" s="14" t="n">
+      <c r="I34" s="44" t="n">
         <v>251218</v>
       </c>
       <c r="J34" s="12" t="inlineStr"/>
@@ -1842,16 +1980,16 @@
           <t>合計</t>
         </is>
       </c>
-      <c r="B35" s="34" t="n"/>
-      <c r="C35" s="34" t="n"/>
-      <c r="D35" s="34" t="n"/>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="35" t="n">
+      <c r="B35" s="51" t="n"/>
+      <c r="C35" s="51" t="n"/>
+      <c r="D35" s="51" t="n"/>
+      <c r="E35" s="52" t="n"/>
+      <c r="F35" s="53" t="n">
         <v>31036676</v>
       </c>
       <c r="G35" s="34" t="n"/>
       <c r="H35" s="34" t="n"/>
-      <c r="I35" s="35" t="n">
+      <c r="I35" s="53" t="n">
         <v>16549801</v>
       </c>
       <c r="J35" s="34" t="inlineStr">
@@ -1891,6 +2029,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="36" t="inlineStr">
         <is>
